--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
@@ -197,7 +197,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1048,7 +1050,7 @@
     <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!B4&amp;" · Provisão de impostos, 13º e férias · "&amp;Config!B6&amp;" de "&amp;Config!B5</f>
         <v/>
@@ -1890,11 +1892,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="K5:M5"/>
     <mergeCell ref="C5:D5"/>
@@ -1955,7 +1958,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -2394,10 +2397,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
@@ -2436,7 +2440,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Entradas e pagamentos do ano</t>
@@ -2732,8 +2736,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Entradas e pagamentos, uma linha por mês: o total que entrou (copie de Entrou no mês do Painel da planilha 09) e o que foi pago de impostos, 13º e férias. Meses não fechados ficam em branco.</t>
+          <t>Em Entradas e pagamentos, uma linha por mês: o total que entrou (copie de Entrou no mês do Painel da planilha 09, sem Outras entradas) e o que foi pago de impostos, 13º e férias. Meses não fechados ficam em branco.</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela do Painel e use o prompt "Preparar a reunião com o contador" da biblioteca do kit para montar a pauta e as perguntas.</t>
+          <t>Copie a tabela do Painel e use o prompt "Caixa 04 · Preparar a reunião mensal com o contador" ou "Caixa 05 · Perguntas sobre a provisão de impostos, 13º e férias" da biblioteca do kit para montar a pauta e as perguntas.</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -1051,9 +1051,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · Provisão de impostos, 13º e férias · "&amp;Config!B6&amp;" de "&amp;Config!B5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Provisão de impostos, 13º e férias · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -1105,32 +1105,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>INDEX(B9:B20,Config!$B$7)</f>
-        <v/>
+        <v>5220</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>INDEX(F9:F20,Config!$B$7)</f>
-        <v/>
+        <v>1573.15555555556</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>INDEX(J9:J20,Config!$B$7)</f>
-        <v/>
+        <v>11320.2</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>INDEX(K9:K20,Config!$B$7)</f>
-        <v/>
+        <v>417.6</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="17">
         <f>INDEX(M9:M20,Config!$B$7)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="19">
+      <c r="K5" s="19" t="str">
         <f>IF(E5&lt;G5,"Atenção: falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="12" t="n"/>
@@ -1217,51 +1217,51 @@
       </c>
       <c r="B9" s="23">
         <f>'Entradas e pagamentos'!B5</f>
-        <v/>
+        <v>21050</v>
       </c>
       <c r="C9" s="23">
         <f>B9*Config!$B$8</f>
-        <v/>
+        <v>1684</v>
       </c>
       <c r="D9" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E9" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F9" s="24">
         <f>SUM(C9:E9)</f>
-        <v/>
+        <v>2839.55555555556</v>
       </c>
       <c r="G9" s="23">
         <f>'Entradas e pagamentos'!F5</f>
-        <v/>
+        <v>1648</v>
       </c>
       <c r="H9" s="23">
         <f>SUM($F$9:F9)</f>
-        <v/>
+        <v>2839.55555555556</v>
       </c>
       <c r="I9" s="23">
         <f>SUM($G$9:G9)</f>
-        <v/>
+        <v>1648</v>
       </c>
       <c r="J9" s="24">
         <f>H9-I9</f>
-        <v/>
+        <v>1191.55555555556</v>
       </c>
       <c r="K9" s="23">
         <f>C9+IF(MOD(1,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(1,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L9" s="25">
+        <v>1684</v>
+      </c>
+      <c r="L9" s="25" t="str">
         <f>IF(J9&lt;K9,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Falta separar</v>
       </c>
       <c r="M9" s="23">
         <f>MAX(0,K9-J9)</f>
-        <v/>
+        <v>492.444444444444</v>
       </c>
     </row>
     <row r="10">
@@ -1272,51 +1272,51 @@
       </c>
       <c r="B10" s="23">
         <f>'Entradas e pagamentos'!B6</f>
-        <v/>
+        <v>23070</v>
       </c>
       <c r="C10" s="23">
         <f>B10*Config!$B$8</f>
-        <v/>
+        <v>1845.6</v>
       </c>
       <c r="D10" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E10" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F10" s="24">
         <f>SUM(C10:E10)</f>
-        <v/>
+        <v>3001.15555555556</v>
       </c>
       <c r="G10" s="23">
         <f>'Entradas e pagamentos'!F6</f>
-        <v/>
+        <v>1684</v>
       </c>
       <c r="H10" s="23">
         <f>SUM($F$9:F10)</f>
-        <v/>
+        <v>5840.71111111111</v>
       </c>
       <c r="I10" s="23">
         <f>SUM($G$9:G10)</f>
-        <v/>
+        <v>3332</v>
       </c>
       <c r="J10" s="24">
         <f>H10-I10</f>
-        <v/>
+        <v>2508.71111111111</v>
       </c>
       <c r="K10" s="23">
         <f>C10+IF(MOD(2,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(2,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L10" s="25">
+        <v>1845.6</v>
+      </c>
+      <c r="L10" s="25" t="str">
         <f>IF(J10&lt;K10,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M10" s="23">
         <f>MAX(0,K10-J10)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1327,51 +1327,51 @@
       </c>
       <c r="B11" s="23">
         <f>'Entradas e pagamentos'!B7</f>
-        <v/>
+        <v>28590</v>
       </c>
       <c r="C11" s="23">
         <f>B11*Config!$B$8</f>
-        <v/>
+        <v>2287.2</v>
       </c>
       <c r="D11" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E11" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F11" s="24">
         <f>SUM(C11:E11)</f>
-        <v/>
+        <v>3442.75555555556</v>
       </c>
       <c r="G11" s="23">
         <f>'Entradas e pagamentos'!F7</f>
-        <v/>
+        <v>1846</v>
       </c>
       <c r="H11" s="23">
         <f>SUM($F$9:F11)</f>
-        <v/>
+        <v>9283.46666666667</v>
       </c>
       <c r="I11" s="23">
         <f>SUM($G$9:G11)</f>
-        <v/>
+        <v>5178</v>
       </c>
       <c r="J11" s="24">
         <f>H11-I11</f>
-        <v/>
+        <v>4105.46666666667</v>
       </c>
       <c r="K11" s="23">
         <f>C11+IF(MOD(3,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(3,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L11" s="25">
+        <v>2287.2</v>
+      </c>
+      <c r="L11" s="25" t="str">
         <f>IF(J11&lt;K11,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M11" s="23">
         <f>MAX(0,K11-J11)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1382,51 +1382,51 @@
       </c>
       <c r="B12" s="23">
         <f>'Entradas e pagamentos'!B8</f>
-        <v/>
+        <v>19760</v>
       </c>
       <c r="C12" s="23">
         <f>B12*Config!$B$8</f>
-        <v/>
+        <v>1580.8</v>
       </c>
       <c r="D12" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E12" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F12" s="24">
         <f>SUM(C12:E12)</f>
-        <v/>
+        <v>2736.35555555556</v>
       </c>
       <c r="G12" s="23">
         <f>'Entradas e pagamentos'!F8</f>
-        <v/>
+        <v>2287</v>
       </c>
       <c r="H12" s="23">
         <f>SUM($F$9:F12)</f>
-        <v/>
+        <v>12019.8222222222</v>
       </c>
       <c r="I12" s="23">
         <f>SUM($G$9:G12)</f>
-        <v/>
+        <v>7465</v>
       </c>
       <c r="J12" s="24">
         <f>H12-I12</f>
-        <v/>
+        <v>4554.82222222222</v>
       </c>
       <c r="K12" s="23">
         <f>C12+IF(MOD(4,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(4,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L12" s="25">
+        <v>1580.8</v>
+      </c>
+      <c r="L12" s="25" t="str">
         <f>IF(J12&lt;K12,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M12" s="23">
         <f>MAX(0,K12-J12)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1437,51 +1437,51 @@
       </c>
       <c r="B13" s="23">
         <f>'Entradas e pagamentos'!B9</f>
-        <v/>
+        <v>31120</v>
       </c>
       <c r="C13" s="23">
         <f>B13*Config!$B$8</f>
-        <v/>
+        <v>2489.6</v>
       </c>
       <c r="D13" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E13" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F13" s="24">
         <f>SUM(C13:E13)</f>
-        <v/>
+        <v>3645.15555555556</v>
       </c>
       <c r="G13" s="23">
         <f>'Entradas e pagamentos'!F9</f>
-        <v/>
+        <v>1581</v>
       </c>
       <c r="H13" s="23">
         <f>SUM($F$9:F13)</f>
-        <v/>
+        <v>15664.9777777778</v>
       </c>
       <c r="I13" s="23">
         <f>SUM($G$9:G13)</f>
-        <v/>
+        <v>9046</v>
       </c>
       <c r="J13" s="24">
         <f>H13-I13</f>
-        <v/>
+        <v>6618.97777777778</v>
       </c>
       <c r="K13" s="23">
         <f>C13+IF(MOD(5,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(5,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L13" s="25">
+        <v>2489.6</v>
+      </c>
+      <c r="L13" s="25" t="str">
         <f>IF(J13&lt;K13,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M13" s="23">
         <f>MAX(0,K13-J13)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1492,51 +1492,51 @@
       </c>
       <c r="B14" s="23">
         <f>'Entradas e pagamentos'!B10</f>
-        <v/>
+        <v>27420</v>
       </c>
       <c r="C14" s="23">
         <f>B14*Config!$B$8</f>
-        <v/>
+        <v>2193.6</v>
       </c>
       <c r="D14" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E14" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F14" s="24">
         <f>SUM(C14:E14)</f>
-        <v/>
+        <v>3349.15555555556</v>
       </c>
       <c r="G14" s="23">
         <f>'Entradas e pagamentos'!F10</f>
-        <v/>
+        <v>2490</v>
       </c>
       <c r="H14" s="23">
         <f>SUM($F$9:F14)</f>
-        <v/>
+        <v>19014.1333333333</v>
       </c>
       <c r="I14" s="23">
         <f>SUM($G$9:G14)</f>
-        <v/>
+        <v>11536</v>
       </c>
       <c r="J14" s="24">
         <f>H14-I14</f>
-        <v/>
+        <v>7478.13333333334</v>
       </c>
       <c r="K14" s="23">
         <f>C14+IF(MOD(6,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(6,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="25">
+        <v>2193.6</v>
+      </c>
+      <c r="L14" s="25" t="str">
         <f>IF(J14&lt;K14,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M14" s="23">
         <f>MAX(0,K14-J14)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1547,51 +1547,51 @@
       </c>
       <c r="B15" s="23">
         <f>'Entradas e pagamentos'!B11</f>
-        <v/>
+        <v>29460</v>
       </c>
       <c r="C15" s="23">
         <f>B15*Config!$B$8</f>
-        <v/>
+        <v>2356.8</v>
       </c>
       <c r="D15" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E15" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F15" s="24">
         <f>SUM(C15:E15)</f>
-        <v/>
+        <v>3512.35555555556</v>
       </c>
       <c r="G15" s="23">
         <f>'Entradas e pagamentos'!F11</f>
-        <v/>
+        <v>2194</v>
       </c>
       <c r="H15" s="23">
         <f>SUM($F$9:F15)</f>
-        <v/>
+        <v>22526.4888888889</v>
       </c>
       <c r="I15" s="23">
         <f>SUM($G$9:G15)</f>
-        <v/>
+        <v>13730</v>
       </c>
       <c r="J15" s="24">
         <f>H15-I15</f>
-        <v/>
+        <v>8796.48888888889</v>
       </c>
       <c r="K15" s="23">
         <f>C15+IF(MOD(7,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(7,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="25">
+        <v>2356.8</v>
+      </c>
+      <c r="L15" s="25" t="str">
         <f>IF(J15&lt;K15,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M15" s="23">
         <f>MAX(0,K15-J15)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1602,51 +1602,51 @@
       </c>
       <c r="B16" s="23">
         <f>'Entradas e pagamentos'!B12</f>
-        <v/>
+        <v>26900</v>
       </c>
       <c r="C16" s="23">
         <f>B16*Config!$B$8</f>
-        <v/>
+        <v>2152</v>
       </c>
       <c r="D16" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E16" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F16" s="24">
         <f>SUM(C16:E16)</f>
-        <v/>
+        <v>3307.55555555556</v>
       </c>
       <c r="G16" s="23">
         <f>'Entradas e pagamentos'!F12</f>
-        <v/>
+        <v>2357</v>
       </c>
       <c r="H16" s="23">
         <f>SUM($F$9:F16)</f>
-        <v/>
+        <v>25834.0444444444</v>
       </c>
       <c r="I16" s="23">
         <f>SUM($G$9:G16)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="J16" s="24">
         <f>H16-I16</f>
-        <v/>
+        <v>9747.04444444444</v>
       </c>
       <c r="K16" s="23">
         <f>C16+IF(MOD(8,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(8,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="25">
+        <v>2152</v>
+      </c>
+      <c r="L16" s="25" t="str">
         <f>IF(J16&lt;K16,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M16" s="23">
         <f>MAX(0,K16-J16)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1657,51 +1657,51 @@
       </c>
       <c r="B17" s="23">
         <f>'Entradas e pagamentos'!B13</f>
-        <v/>
+        <v>5220</v>
       </c>
       <c r="C17" s="23">
         <f>B17*Config!$B$8</f>
-        <v/>
+        <v>417.6</v>
       </c>
       <c r="D17" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E17" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F17" s="24">
         <f>SUM(C17:E17)</f>
-        <v/>
+        <v>1573.15555555556</v>
       </c>
       <c r="G17" s="23">
         <f>'Entradas e pagamentos'!F13</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H17" s="23">
         <f>SUM($F$9:F17)</f>
-        <v/>
+        <v>27407.2</v>
       </c>
       <c r="I17" s="23">
         <f>SUM($G$9:G17)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="J17" s="24">
         <f>H17-I17</f>
-        <v/>
+        <v>11320.2</v>
       </c>
       <c r="K17" s="23">
         <f>C17+IF(MOD(9,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(9,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="25">
+        <v>417.6</v>
+      </c>
+      <c r="L17" s="25" t="str">
         <f>IF(J17&lt;K17,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M17" s="23">
         <f>MAX(0,K17-J17)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1712,51 +1712,51 @@
       </c>
       <c r="B18" s="23">
         <f>'Entradas e pagamentos'!B14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C18" s="23">
         <f>B18*Config!$B$8</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D18" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E18" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F18" s="24">
         <f>SUM(C18:E18)</f>
-        <v/>
+        <v>1155.55555555556</v>
       </c>
       <c r="G18" s="23">
         <f>'Entradas e pagamentos'!F14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H18" s="23">
         <f>SUM($F$9:F18)</f>
-        <v/>
+        <v>28562.7555555556</v>
       </c>
       <c r="I18" s="23">
         <f>SUM($G$9:G18)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="J18" s="24">
         <f>H18-I18</f>
-        <v/>
+        <v>12475.7555555556</v>
       </c>
       <c r="K18" s="23">
         <f>C18+IF(MOD(10,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(10,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L18" s="25">
+        <v>0</v>
+      </c>
+      <c r="L18" s="25" t="str">
         <f>IF(J18&lt;K18,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M18" s="23">
         <f>MAX(0,K18-J18)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1767,51 +1767,51 @@
       </c>
       <c r="B19" s="23">
         <f>'Entradas e pagamentos'!B15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C19" s="23">
         <f>B19*Config!$B$8</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D19" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E19" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F19" s="24">
         <f>SUM(C19:E19)</f>
-        <v/>
+        <v>1155.55555555556</v>
       </c>
       <c r="G19" s="23">
         <f>'Entradas e pagamentos'!F15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H19" s="23">
         <f>SUM($F$9:F19)</f>
-        <v/>
+        <v>29718.3111111111</v>
       </c>
       <c r="I19" s="23">
         <f>SUM($G$9:G19)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="J19" s="24">
         <f>H19-I19</f>
-        <v/>
+        <v>13631.3111111111</v>
       </c>
       <c r="K19" s="23">
         <f>C19+IF(MOD(11,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(11,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="25">
+        <v>12000</v>
+      </c>
+      <c r="L19" s="25" t="str">
         <f>IF(J19&lt;K19,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M19" s="23">
         <f>MAX(0,K19-J19)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1822,51 +1822,51 @@
       </c>
       <c r="B20" s="23">
         <f>'Entradas e pagamentos'!B16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C20" s="23">
         <f>B20*Config!$B$8</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D20" s="23">
         <f>Config!$E$24</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E20" s="23">
         <f>Config!$F$24</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
       <c r="F20" s="24">
         <f>SUM(C20:E20)</f>
-        <v/>
+        <v>1155.55555555556</v>
       </c>
       <c r="G20" s="23">
         <f>'Entradas e pagamentos'!F16</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H20" s="23">
         <f>SUM($F$9:F20)</f>
-        <v/>
+        <v>30873.8666666667</v>
       </c>
       <c r="I20" s="23">
         <f>SUM($G$9:G20)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="J20" s="24">
         <f>H20-I20</f>
-        <v/>
+        <v>14786.8666666667</v>
       </c>
       <c r="K20" s="23">
         <f>C20+IF(MOD(12,12)+1=MATCH(Config!$B$11,Config!$H$5:$H$16,0),Config!$E$25,0)+IF(MOD(12,12)+1=MATCH(Config!$B$12,Config!$H$5:$H$16,0),Config!$F$25,0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="25">
+        <v>1866.66666666667</v>
+      </c>
+      <c r="L20" s="25" t="str">
         <f>IF(J20&lt;K20,"Falta separar","Coberto")</f>
-        <v/>
+        <v>Coberto</v>
       </c>
       <c r="M20" s="23">
         <f>MAX(0,K20-J20)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B7" s="25">
         <f>MATCH(B6,$H$5:$H$16,0)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="H7" s="30" t="inlineStr">
         <is>
@@ -2213,11 +2213,11 @@
       </c>
       <c r="E16" s="34">
         <f>IF(OR(A16="",C16&lt;&gt;"Sim"),0,B16/12*(1+$B$10))</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="F16" s="34">
         <f>IF(OR(A16="",D16&lt;&gt;"Sim"),0,B16*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H16" s="30" t="inlineStr">
         <is>
@@ -2246,11 +2246,11 @@
       </c>
       <c r="E17" s="34">
         <f>IF(OR(A17="",C17&lt;&gt;"Sim"),0,B17/12*(1+$B$10))</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="F17" s="34">
         <f>IF(OR(A17="",D17&lt;&gt;"Sim"),0,B17*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2274,11 +2274,11 @@
       </c>
       <c r="E18" s="34">
         <f>IF(OR(A18="",C18&lt;&gt;"Sim"),0,B18/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F18" s="34">
         <f>IF(OR(A18="",D18&lt;&gt;"Sim"),0,B18*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
     </row>
     <row r="19">
@@ -2288,11 +2288,11 @@
       <c r="D19" s="29" t="n"/>
       <c r="E19" s="34">
         <f>IF(OR(A19="",C19&lt;&gt;"Sim"),0,B19/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F19" s="34">
         <f>IF(OR(A19="",D19&lt;&gt;"Sim"),0,B19*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2302,11 +2302,11 @@
       <c r="D20" s="29" t="n"/>
       <c r="E20" s="34">
         <f>IF(OR(A20="",C20&lt;&gt;"Sim"),0,B20/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F20" s="34">
         <f>IF(OR(A20="",D20&lt;&gt;"Sim"),0,B20*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2316,11 +2316,11 @@
       <c r="D21" s="29" t="n"/>
       <c r="E21" s="34">
         <f>IF(OR(A21="",C21&lt;&gt;"Sim"),0,B21/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F21" s="34">
         <f>IF(OR(A21="",D21&lt;&gt;"Sim"),0,B21*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2330,11 +2330,11 @@
       <c r="D22" s="29" t="n"/>
       <c r="E22" s="34">
         <f>IF(OR(A22="",C22&lt;&gt;"Sim"),0,B22/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F22" s="34">
         <f>IF(OR(A22="",D22&lt;&gt;"Sim"),0,B22*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2344,11 +2344,11 @@
       <c r="D23" s="29" t="n"/>
       <c r="E23" s="34">
         <f>IF(OR(A23="",C23&lt;&gt;"Sim"),0,B23/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F23" s="34">
         <f>IF(OR(A23="",D23&lt;&gt;"Sim"),0,B23*(1+$B$9)/12*(1+$B$10))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2359,11 +2359,11 @@
       </c>
       <c r="E24" s="36">
         <f>SUM(E16:E23)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="F24" s="36">
         <f>SUM(F16:F23)</f>
-        <v/>
+        <v>155.555555555556</v>
       </c>
     </row>
     <row r="25">
@@ -2374,11 +2374,11 @@
       </c>
       <c r="E25" s="36">
         <f>E24*12</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="F25" s="36">
         <f>F24*12</f>
-        <v/>
+        <v>1866.66666666667</v>
       </c>
     </row>
     <row r="27">
@@ -2429,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2450,7 +2450,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Amarelo: o que entrou no caixa em cada mês (total do Painel da planilha 09) e o que foi efetivamente pago de impostos, 13º e férias.</t>
+          <t>Amarelo: o que entrou no caixa em cada mês (Entrou no mês do Painel da planilha 09, sem a categoria Outras entradas) e o que foi efetivamente pago de impostos, 13º e férias.</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>33660</v>
+        <v>21050</v>
       </c>
       <c r="C5" s="33" t="n">
         <v>1648</v>
@@ -2502,7 +2502,7 @@
       <c r="E5" s="33" t="n"/>
       <c r="F5" s="34">
         <f>SUM(C5:E5)</f>
-        <v/>
+        <v>1648</v>
       </c>
     </row>
     <row r="6">
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="B6" s="33" t="n">
-        <v>14000</v>
+        <v>23070</v>
       </c>
       <c r="C6" s="33" t="n">
-        <v>2693</v>
+        <v>1684</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="34">
         <f>SUM(C6:E6)</f>
-        <v/>
+        <v>1684</v>
       </c>
     </row>
     <row r="7">
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>19560</v>
+        <v>28590</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1120</v>
+        <v>1846</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="34">
         <f>SUM(C7:E7)</f>
-        <v/>
+        <v>1846</v>
       </c>
     </row>
     <row r="8">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>20420</v>
+        <v>19760</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>1565</v>
+        <v>2287</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="34">
         <f>SUM(C8:E8)</f>
-        <v/>
+        <v>2287</v>
       </c>
     </row>
     <row r="9">
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="B9" s="33" t="n">
-        <v>19200</v>
+        <v>31120</v>
       </c>
       <c r="C9" s="33" t="n">
-        <v>1634</v>
+        <v>1581</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="34">
         <f>SUM(C9:E9)</f>
-        <v/>
+        <v>1581</v>
       </c>
     </row>
     <row r="10">
@@ -2588,16 +2588,16 @@
         </is>
       </c>
       <c r="B10" s="33" t="n">
-        <v>25970</v>
+        <v>27420</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1536</v>
+        <v>2490</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="34">
         <f>SUM(C10:E10)</f>
-        <v/>
+        <v>2490</v>
       </c>
     </row>
     <row r="11">
@@ -2607,16 +2607,16 @@
         </is>
       </c>
       <c r="B11" s="33" t="n">
-        <v>30170</v>
+        <v>29460</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>2078</v>
+        <v>2194</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="34">
         <f>SUM(C11:E11)</f>
-        <v/>
+        <v>2194</v>
       </c>
     </row>
     <row r="12">
@@ -2626,16 +2626,16 @@
         </is>
       </c>
       <c r="B12" s="33" t="n">
-        <v>26660</v>
+        <v>26900</v>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2414</v>
+        <v>2357</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="34">
         <f>SUM(C12:E12)</f>
-        <v/>
+        <v>2357</v>
       </c>
     </row>
     <row r="13">
@@ -2645,14 +2645,14 @@
         </is>
       </c>
       <c r="B13" s="33" t="n">
-        <v>10800</v>
+        <v>5220</v>
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n"/>
       <c r="F13" s="34">
         <f>SUM(C13:E13)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2667,7 +2667,7 @@
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="34">
         <f>SUM(C14:E14)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2682,7 +2682,7 @@
       <c r="E15" s="33" t="n"/>
       <c r="F15" s="34">
         <f>SUM(C15:E15)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2697,7 +2697,7 @@
       <c r="E16" s="33" t="n"/>
       <c r="F16" s="34">
         <f>SUM(C16:E16)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2708,29 +2708,36 @@
       </c>
       <c r="B17" s="36">
         <f>SUM(B5:B16)</f>
-        <v/>
+        <v>212590</v>
       </c>
       <c r="C17" s="36">
         <f>SUM(C5:C16)</f>
-        <v/>
+        <v>16087</v>
       </c>
       <c r="D17" s="36">
         <f>SUM(D5:D16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E17" s="36">
         <f>SUM(E5:E16)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F17" s="36">
         <f>SUM(F5:F16)</f>
-        <v/>
+        <v>16087</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>Deixe em branco os meses que ainda não fecharam. Impostos pagos: o valor das guias quitadas no mês (no exemplo, a guia de setembro ainda não foi paga: ver planilha 09).</t>
+          <t>Deixe em branco os meses que ainda não fecharam. Impostos pagos: o valor das guias quitadas no mês (no exemplo, a guia de setembro ainda não foi paga: ver planilha 09). Setembro mostra o que entrou até 11/09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Entradas recebidas = Entrou no mês (Painel da 09) menos "Outras entradas" (no exemplo, a devolução de despesa pessoal de abril, R$ 480, que não é receita e não paga imposto).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
@@ -843,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1004,17 +1004,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/10-provisao-de-impostos.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:M20">
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>ROW()-9+1=Config!$B$7</formula>
+      <formula>ROW()-9+1=INDIRECT("Config!$B$7")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J20">
